--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -6,7 +6,10 @@
     <sheet name="Room Specs" sheetId="1" r:id="rId1"/>
     <sheet name="G-10" sheetId="2" r:id="rId2"/>
     <sheet name="G-05" sheetId="3" r:id="rId3"/>
-    <sheet name="Pattern Guide" sheetId="4" r:id="rId4"/>
+    <sheet name="SL-01" sheetId="4" r:id="rId4"/>
+    <sheet name="SH-01" sheetId="5" r:id="rId5"/>
+    <sheet name="AUD-01" sheetId="6" r:id="rId6"/>
+    <sheet name="Pattern Guide" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,82 +416,100 @@
         <v>Projector (Yes or No)</v>
       </c>
       <c r="D1" t="str">
-        <v>No. of Computers</v>
+        <v>No. of Computers / Equipment</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Room Category</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>G-10</v>
-      </c>
-      <c r="B2">
-        <v>50</v>
+        <v>Lecture Rooms / Halls</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>G-11</v>
+        <v>G-10</v>
       </c>
       <c r="B3">
         <v>50</v>
       </c>
       <c r="C3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="D3">
         <v>0</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Lecture Hall</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>F-04</v>
+        <v>G-11</v>
       </c>
       <c r="B4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C4" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="D4">
         <v>0</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Lecture Hall</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Labs</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
+        <v>F-04</v>
+      </c>
+      <c r="B5">
+        <v>60</v>
       </c>
       <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
+        <v>Yes</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Lecture Hall</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>G-05</v>
-      </c>
-      <c r="B6">
-        <v>40</v>
+        <v>Computer Labs</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="D6">
-        <v>40</v>
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>G-16</v>
+        <v>G-05</v>
       </c>
       <c r="B7">
         <v>40</v>
@@ -499,10 +520,149 @@
       <c r="D7">
         <v>40</v>
       </c>
+      <c r="E7" t="str">
+        <v>Computer Lab</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>G-16</v>
+      </c>
+      <c r="B8">
+        <v>40</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Computer Lab</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Science Labs</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SL-01</v>
+      </c>
+      <c r="B10">
+        <v>35</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Science Lab</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SL-02</v>
+      </c>
+      <c r="B11">
+        <v>35</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D11">
+        <v>12</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Science Lab</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Seminar Halls</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SH-01</v>
+      </c>
+      <c r="B13">
+        <v>120</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Seminar Hall</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Auditoriums</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AUD-01</v>
+      </c>
+      <c r="B15">
+        <v>300</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Auditorium</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -879,11 +1039,566 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:I6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>UET KSK Timetable Excel Pattern Guide</v>
+        <v>Day / Time</v>
+      </c>
+      <c r="B1" t="str">
+        <v>8-9 AM</v>
+      </c>
+      <c r="C1" t="str">
+        <v>9-10 AM</v>
+      </c>
+      <c r="D1" t="str">
+        <v>10-11 AM</v>
+      </c>
+      <c r="E1" t="str">
+        <v>11-12 AM</v>
+      </c>
+      <c r="F1" t="str">
+        <v>12-1 PM (Break)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>1-2 PM</v>
+      </c>
+      <c r="H1" t="str">
+        <v>2-3 PM</v>
+      </c>
+      <c r="I1" t="str">
+        <v>3-4 PM</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Physics Lab | Sem 1-A</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Physics Lab | Sem 1-A</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Lunch Break</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Chemistry Lab | Sem 1-A</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Chemistry Lab | Sem 1-A</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Circuit Analysis Lab | Sem 3-A</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Circuit Analysis Lab | Sem 3-A</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Applied Physics Lab | Sem 1-B</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Applied Physics Lab | Sem 1-B</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Lunch Break</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Environmental Eng Lab | Sem 5-A</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Environmental Eng Lab | Sem 5-A</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Jummah Break</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Day / Time</v>
+      </c>
+      <c r="B1" t="str">
+        <v>8-9 AM</v>
+      </c>
+      <c r="C1" t="str">
+        <v>9-10 AM</v>
+      </c>
+      <c r="D1" t="str">
+        <v>10-11 AM</v>
+      </c>
+      <c r="E1" t="str">
+        <v>11-12 AM</v>
+      </c>
+      <c r="F1" t="str">
+        <v>12-1 PM (Break)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>1-2 PM</v>
+      </c>
+      <c r="H1" t="str">
+        <v>2-3 PM</v>
+      </c>
+      <c r="I1" t="str">
+        <v>3-4 PM</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Department Orientation Seminar | Sem 1-A</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Department Orientation Seminar | Sem 1-A</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Lunch Break</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Guest Speaker Lecture | Sem 5-A</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Guest Speaker Lecture | Sem 5-A</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="str">
+        <v>FYP Progress Workshop | Sem 7-A</v>
+      </c>
+      <c r="E4" t="str">
+        <v>FYP Progress Workshop | Sem 7-A</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Lunch Break</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Industry Tech Talk | Sem 3-A</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Industry Tech Talk | Sem 3-A</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Jummah Break</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Day / Time</v>
+      </c>
+      <c r="B1" t="str">
+        <v>8-9 AM</v>
+      </c>
+      <c r="C1" t="str">
+        <v>9-10 AM</v>
+      </c>
+      <c r="D1" t="str">
+        <v>10-11 AM</v>
+      </c>
+      <c r="E1" t="str">
+        <v>11-12 AM</v>
+      </c>
+      <c r="F1" t="str">
+        <v>12-1 PM (Break)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>1-2 PM</v>
+      </c>
+      <c r="H1" t="str">
+        <v>2-3 PM</v>
+      </c>
+      <c r="I1" t="str">
+        <v>3-4 PM</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Lunch Break</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Campus Welcome Ceremony | Sem 1-A</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Campus Welcome Ceremony | Sem 1-A</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Campus Welcome Ceremony | Sem 1-A</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Lunch Break</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Annual Research Symposium | Sem 7-A</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Annual Research Symposium | Sem 7-A</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Jummah Break</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A21"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>UET KSK Timetable Excel Pattern Guide (All 5 Room Categories)</v>
       </c>
     </row>
     <row r="2">
@@ -898,82 +1613,97 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>- Column 1: Room No (e.g. G-10, G-11, F-04, G-05)</v>
+        <v>- Column A (Room No.): Enter Room Code (e.g. G-10, G-05, SL-01, SH-01, AUD-01)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>- Column 2: No. of Chairs (e.g. 50, 60, 40)</v>
+        <v>- Column B (No. of Chairs): Seating capacity (e.g. 50 for Lecture Hall, 40 for Computer Lab, 35 for Science Lab, 120 for Seminar Hall, 300 for Auditorium)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>- Column 3: Projector Available ('Yes' or 'No')</v>
+        <v>- Column C (Projector): Enter 'Yes' or 'No'</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>- Column 4: No. of Computers (For Labs, e.g. 40; for lecture halls set 0 or leave blank)</v>
+        <v>- Column D (No. of Computers / Equipment): Enter count of computers or lab equipment stations (e.g. 40 for Computer Lab, 10 for Science Lab, 0 for Lecture Hall/Hall)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>- Note: Use 'Labs' in Column 1 to start the computer labs section.</v>
+        <v>- Column E (Room Category): MUST specify room category: 'Lecture Hall', 'Computer Lab', 'Science Lab', 'Seminar Hall', or 'Auditorium'</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>- Section Headers: You can also use section header rows in Column A like 'Lecture Rooms / Halls', 'Computer Labs', 'Science Labs', 'Seminar Halls', 'Auditoriums' to automatically assign categories!</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sheets 2+: Room Timetable Matrix (One sheet per room name, e.g. 'G-10', 'G-05')</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>- Header Row (Row 1): 'Day / Time', '8-9 AM', '9-10 AM', '10-11 AM', '11-12 AM', '12-1 PM', '1-2 PM', '2-3 PM', '3-4 PM'</v>
+        <v>Sheets 2+: Room Timetable Matrices (One matrix sheet per room, e.g. 'G-10', 'G-05', 'SL-01', 'SH-01', 'AUD-01')</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>- Column 1 (Days): Monday, Tuesday, Wednesday, Thursday, Friday</v>
+        <v>- Header Row (Row 1): 'Day / Time', '8-9 AM', '9-10 AM', '10-11 AM', '11-12 AM', '12-1 PM (Break)', '1-2 PM', '2-3 PM', '3-4 PM'</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>- Cell Format: Enter lecture details in cell format: Course Name | Sem [Semester]-[Section]</v>
+        <v>- Column 1 (Days): Monday, Tuesday, Wednesday, Thursday, Friday</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve">  Example 1: Programming Fundamentals | Sem 1-A</v>
+        <v>- Cell Format: Enter lecture details in exact format: Course Name | Sem [Semester]-[Section]</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">  Example 2: Data Structures | Sem 3-B</v>
+        <v xml:space="preserve">  Example 1 (Lecture Hall G-10): Programming Fundamentals | Sem 1-A</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>- (Note: Enter 1 or 'Yes' if you want default course &amp; section assigned)</v>
+        <v xml:space="preserve">  Example 2 (Computer Lab G-05): Data Structures Lab | Sem 3-A</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v xml:space="preserve">  Example 3 (Science Lab SL-01): Physics Lab | Sem 1-A</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>After filling out this template, upload the file in the UET KSK Timetable Portal!</v>
+        <v xml:space="preserve">  Example 4 (Seminar Hall SH-01): Department Orientation Seminar | Sem 1-A</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve">  Example 5 (Auditorium AUD-01): Campus Welcome Ceremony | Sem 1-A</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Upload this spreadsheet in the UET KSK Timetable Portal to update room specifications and timetable schedule slots!</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A21"/>
   </ignoredErrors>
 </worksheet>
 </file>